--- a/astro-site/public/dl/kit-tareas-hamburgueseria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/04-tareas-perfiles.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Parrillero" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cocinero Línea" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Freidurista" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Encargado" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Camarero" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parrillero" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocinero Línea" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freidurista" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encargado" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camarero" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Parrillero'!$A$1:$G$25</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Cocinero Línea'!$A$1:$G$22</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Freidurista'!$A$1:$G$21</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Encargado'!$A$1:$G$25</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Camarero'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Parrillero'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cocinero Línea'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidurista'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Encargado'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Camarero'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +84,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -142,44 +147,60 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -539,15 +560,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -555,6 +577,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -562,6 +585,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -569,6 +593,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -576,8 +601,33 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -591,16 +641,16 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tareas Diarias — Parrillero / Grill Master</t>
@@ -614,10 +664,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -642,7 +693,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -659,10 +710,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -688,10 +737,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -717,10 +764,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -746,10 +791,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -782,10 +825,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -811,10 +852,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -840,10 +879,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -869,10 +906,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -898,10 +933,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -934,10 +967,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -963,10 +994,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -992,10 +1021,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1020,6 +1047,7 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="14" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="C21" s="15" t="inlineStr">
         <is>
@@ -1028,14 +1056,19 @@
       </c>
       <c r="D21" s="16">
         <f>COUNTIF(F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>de 12</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F21">
+        <f>COUNTIF(B5:B19,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -1043,6 +1076,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
@@ -1060,7 +1094,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1075,16 +1119,16 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tareas Diarias — Cocinero de Línea / Montaje</t>
@@ -1098,10 +1142,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1126,7 +1171,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1143,10 +1188,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1172,10 +1215,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1201,10 +1242,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1230,10 +1269,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1266,10 +1303,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1295,10 +1330,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1324,10 +1357,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1360,10 +1391,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1389,10 +1418,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -1417,6 +1444,7 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="10" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="C18" s="15" t="inlineStr">
         <is>
@@ -1425,14 +1453,19 @@
       </c>
       <c r="D18" s="16">
         <f>COUNTIF(F5:F16,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>de 9</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -1440,6 +1473,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
@@ -1457,7 +1491,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1472,16 +1516,16 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tareas Diarias — Freidurista</t>
@@ -1495,10 +1539,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1523,7 +1568,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1540,10 +1585,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1569,10 +1612,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1605,10 +1646,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1634,10 +1673,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -1663,10 +1700,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1692,10 +1727,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1728,10 +1761,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1757,10 +1788,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1785,6 +1814,7 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="C17" s="15" t="inlineStr">
         <is>
@@ -1793,14 +1823,19 @@
       </c>
       <c r="D17" s="16">
         <f>COUNTIF(F5:F15,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>de 8</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F17">
+        <f>COUNTIF(B5:B15,"?*")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -1808,6 +1843,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
@@ -1821,11 +1857,21 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A21:G21"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F9 F10 F11 F12 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1840,16 +1886,16 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tareas Diarias — Encargado/a</t>
@@ -1863,10 +1909,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1891,7 +1938,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1908,10 +1955,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1937,10 +1982,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1966,10 +2009,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1995,10 +2036,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -2024,10 +2063,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -2060,10 +2097,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -2089,10 +2124,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -2118,10 +2151,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -2154,10 +2185,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -2183,10 +2212,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -2212,10 +2239,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2241,10 +2266,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -2269,6 +2292,7 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="14" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="C21" s="15" t="inlineStr">
         <is>
@@ -2277,14 +2301,19 @@
       </c>
       <c r="D21" s="16">
         <f>COUNTIF(F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>de 12</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F21">
+        <f>COUNTIF(B5:B19,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -2292,6 +2321,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
@@ -2309,7 +2339,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -2324,16 +2364,16 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tareas Diarias — Camarero/a</t>
@@ -2347,10 +2387,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2375,7 +2416,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2392,10 +2433,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -2421,10 +2460,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -2450,10 +2487,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -2486,10 +2521,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -2515,10 +2548,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -2544,10 +2575,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -2573,10 +2602,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -2602,10 +2629,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -2631,10 +2656,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -2667,10 +2690,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -2696,10 +2717,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -2724,6 +2743,7 @@
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="10" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="C20" s="15" t="inlineStr">
         <is>
@@ -2732,14 +2752,19 @@
       </c>
       <c r="D20" s="16">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>de 11</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F20">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
@@ -2747,6 +2772,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
@@ -2764,7 +2790,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F13 F14 F15 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/04-tareas-perfiles.xlsx
@@ -15,10 +15,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camarero" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Parrillero'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Parrillero'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cocinero Línea'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cocinero Línea'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Freidurista'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidurista'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Encargado'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Encargado'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Camarero'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Camarero'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -636,7 +641,7 @@
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1104,8 +1109,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1114,7 +1127,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1501,8 +1514,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1511,7 +1532,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1871,8 +1892,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1881,7 +1910,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2349,8 +2378,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2359,7 +2396,7 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2800,7 +2837,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/04-tareas-perfiles.xlsx
@@ -15,16 +15,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camarero" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Parrillero'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Parrillero'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Parrillero'!$A$1:$G$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cocinero Línea'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cocinero Línea'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cocinero Línea'!$A$1:$G$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Freidurista'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidurista'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidurista'!$A$1:$G$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Encargado'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Encargado'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Encargado'!$A$1:$G$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Camarero'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Camarero'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Camarero'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +96,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +142,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -154,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +210,49 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,58 +630,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Tareas por Perfil Profesional — Hamburguesería</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Cada pestaña = un perfil de tu hamburguesería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Entrega una copia a cada miembro del equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = pendiente · ✓ = completada</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>▸ Estás en 04-tareas-perfiles.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -643,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -693,7 +860,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -708,404 +875,469 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Encender plancha y precalentar</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Sacar carne de cámara y temperar</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Preparar prensa smash y espátulas</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Pre-cocinar bacon si aplica</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Cocinar patties según comanda y punto solicitado</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Smash: prensar bola en plancha caliente 30-45s</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Fundir queso con campana</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Tostar pan en plancha</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Mantener plancha limpia entre tandas</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Limpiar plancha a fondo</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Guardar carne sobrante etiquetada</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Preparar patties para mañana si aplica</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Parrillero</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
     <row r="21">
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D21" s="16">
-        <f>COUNTIF(F5:F19,"✓")</f>
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D26" s="16">
+        <f>COUNTIFS(B5:B24,"?*",F5:F24,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F21">
-        <f>COUNTIF(B5:B19,"?*")</f>
+      <c r="F26">
+        <f>COUNTIF(B5:B24,"?*")-COUNTIF(F5:F24,"N/A")</f>
         <v>12.0</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G19">
+  <conditionalFormatting sqref="A5:G24">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1129,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1179,7 +1411,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1194,323 +1426,388 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Preparar toppings en inserts</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Preparar salsas en biberones</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Cortar quesos en lonchas</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Montar línea ordenada</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Montar burgers según comanda</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Reponer inserts constantemente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Empaquetar take-away y delivery</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Cubrir y refrigerar inserts</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Limpiar línea</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
     <row r="18">
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D18" s="16">
-        <f>COUNTIF(F5:F16,"✓")</f>
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D23" s="16">
+        <f>COUNTIFS(B5:B21,"?*",F5:F21,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F18">
-        <f>COUNTIF(B5:B16,"?*")</f>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")-COUNTIF(F5:F21,"N/A")</f>
         <v>9.0</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A27:G27"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G16">
+  <conditionalFormatting sqref="A5:G21">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1534,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1584,7 +1881,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1599,296 +1896,361 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Encender freidora, verificar aceite</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Preparar patatas y sides</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Freír patatas por tandas</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Freír sides: aros, nuggets, jalapeños</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Salar y condimentar al sacar</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Emplatar en cesta/cucurucho</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Apagar y limpiar freidora</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Filtrar aceite</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Freidurista</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n"/>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
     <row r="17">
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D17" s="16">
-        <f>COUNTIF(F5:F15,"✓")</f>
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D22" s="16">
+        <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F17">
-        <f>COUNTIF(B5:B15,"?*")</f>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
         <v>8.0</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A21:G21"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G15">
+  <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F9 F10 F11 F12 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F9 F10 F11 F12 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1912,7 +2274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1962,7 +2324,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1977,404 +2339,469 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Abrir local, desactivar alarma</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Verificar equipo</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Briefing equipo</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Encender tablets delivery</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Preparar caja</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Supervisar tiempos y calidad</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Gestionar delivery</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Resolver incidencias</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Supervisar cierre</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Cuadrar caja</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Pedidos mañana</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Cerrar local</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
     <row r="21">
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D21" s="16">
-        <f>COUNTIF(F5:F19,"✓")</f>
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D26" s="16">
+        <f>COUNTIFS(B5:B24,"?*",F5:F24,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F21">
-        <f>COUNTIF(B5:B19,"?*")</f>
+      <c r="F26">
+        <f>COUNTIF(B5:B24,"?*")-COUNTIF(F5:F24,"N/A")</f>
         <v>12.0</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G19">
+  <conditionalFormatting sqref="A5:G24">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F16 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2398,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2448,7 +2875,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2463,377 +2890,442 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Montar mesas</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Reponer condimentos: kétchup, mostaza, tabasco, sal</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Verificar carta y promos del día</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Recibir y acomodar clientes</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Tomar comandas (punto de carne, alérgenos)</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Servir burgers y sides</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Sugerir combos y extras</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Limpiar mesa rápido entre clientes</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Cobrar</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Desmontar y limpiar mesas</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Reponer condimentos para mañana</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
     <row r="20">
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D20" s="16">
-        <f>COUNTIF(F5:F18,"✓")</f>
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D25" s="16">
+        <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20">
-        <f>COUNTIF(B5:B18,"?*")</f>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
         <v>11.0</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G18">
+  <conditionalFormatting sqref="A5:G23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F13 F14 F15 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
